--- a/Dataset_2/4_Integration_results/Stats_table_region.xlsx
+++ b/Dataset_2/4_Integration_results/Stats_table_region.xlsx
@@ -419,19 +419,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>25.2</v>
+        <v>22.4</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -439,19 +439,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000028156285394402</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000310865368934475</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000028156285394402</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000310865368934475</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000000000000000000000000147911202933834</v>
+        <v>0.000000000000000000000000000000000000000000000000000157058223220615</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000028156285394402</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000270827303193483</v>
       </c>
     </row>
     <row r="4">
@@ -459,17 +459,17 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>25.8</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>25.8</v>
+        <v>23</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F4" t="n">
         <v>23</v>
-      </c>
-      <c r="F4" t="n">
-        <v>25.8</v>
       </c>
     </row>
     <row r="5">
@@ -477,19 +477,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.000000000000000000000000000000000000000000000000366708077510506</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000014011375119321</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000000000000000000000000000000000000000000000000366708077510506</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000014011375119321</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00774333191191681</v>
+        <v>0.00132748175625966</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000000000000000000000000000000000000000000000000366708077510506</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000014011375119321</v>
       </c>
     </row>
     <row r="6">
@@ -497,17 +497,17 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>22.8</v>
+        <v>21.1</v>
       </c>
       <c r="C6" t="n">
-        <v>22.8</v>
+        <v>21.1</v>
       </c>
       <c r="D6"/>
       <c r="E6" t="n">
-        <v>23.9</v>
+        <v>21.5</v>
       </c>
       <c r="F6" t="n">
-        <v>22.8</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="7">
@@ -515,19 +515,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000303319995139598</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000417720374227167</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000303319995139598</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000417720374227167</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0000000000000000000000000000000000000662404772403981</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000111094974988701</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000303319995139598</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000417720374227167</v>
       </c>
     </row>
     <row r="8">
@@ -535,17 +535,17 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="D8"/>
       <c r="E8" t="n">
-        <v>22.8</v>
+        <v>21.8</v>
       </c>
       <c r="F8" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -553,19 +553,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0000000677903594395501</v>
+        <v>0.000000000000000000000000141840580111466</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0000000677903594395501</v>
+        <v>0.000000000000000000000000141840580111466</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0073466608990165</v>
+        <v>0.0000000000447380731842182</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0000000677903594395501</v>
+        <v>0.000000000000000000000000141840580111466</v>
       </c>
     </row>
     <row r="10">
@@ -573,17 +573,17 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>43.3</v>
+        <v>38.8</v>
       </c>
       <c r="C10" t="n">
-        <v>43.3</v>
+        <v>38.8</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="n">
-        <v>39.8</v>
+        <v>35.6</v>
       </c>
       <c r="F10" t="n">
-        <v>43.3</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="11">
@@ -591,19 +591,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0000000000000000000000000000000000000000000394524802944234</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000142726595016798</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0000000000000000000000000000000000000000000394524802944234</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000142726595016798</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00000000000000283224985355773</v>
+        <v>0.000000000000000000000000000000293846186365235</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0000000000000000000000000000000000000000000394524802944234</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000107043583022375</v>
       </c>
     </row>
     <row r="12">
@@ -611,17 +611,17 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>30.9</v>
+        <v>28.7</v>
       </c>
       <c r="C12" t="n">
-        <v>30.9</v>
+        <v>28.7</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="F12" t="n">
-        <v>30.9</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="13">
@@ -629,19 +629,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000303319995139598</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000249285234858136</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000303319995139598</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000249285234858136</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00000030723815555902</v>
+        <v>0.0000000000322153383887232</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000303319995139598</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000249285234858136</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_2/4_Integration_results/Stats_table_region.xlsx
+++ b/Dataset_2/4_Integration_results/Stats_table_region.xlsx
@@ -419,19 +419,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="E2" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="3">
@@ -439,19 +439,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000310865368934475</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000104425365702883</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000310865368934475</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000104425365702883</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000157058223220615</v>
+        <v>0.0000000000000000000000000000000000000000000000266095433088263</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000270827303193483</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000911846435017811</v>
       </c>
     </row>
     <row r="4">
@@ -459,17 +459,17 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>23.9</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>23.9</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="5">
@@ -477,19 +477,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000014011375119321</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000168687568312926</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000014011375119321</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000168687568312926</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00132748175625966</v>
+        <v>0.000703173717046452</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000014011375119321</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000168687568312926</v>
       </c>
     </row>
     <row r="6">
@@ -497,17 +497,17 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="D6"/>
       <c r="E6" t="n">
-        <v>21.5</v>
+        <v>22.3</v>
       </c>
       <c r="F6" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -515,19 +515,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000417720374227167</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000408041510078157</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000417720374227167</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000408041510078157</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000111094974988701</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000605606777347101</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000417720374227167</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000408041510078157</v>
       </c>
     </row>
     <row r="8">
@@ -535,17 +535,17 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>22.8</v>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>22.8</v>
       </c>
       <c r="D8"/>
       <c r="E8" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="9">
@@ -553,19 +553,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>0.000000000000000000000000141840580111466</v>
+        <v>0.0000000000000000000000552597957019121</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000000000000000000000000141840580111466</v>
+        <v>0.0000000000000000000000552597957019121</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0000000000447380731842182</v>
+        <v>0.0000000000541083275416263</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000000000000000000000000141840580111466</v>
+        <v>0.0000000000000000000000552597957019121</v>
       </c>
     </row>
     <row r="10">
@@ -573,17 +573,17 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>38.8</v>
+        <v>39.8</v>
       </c>
       <c r="C10" t="n">
-        <v>38.8</v>
+        <v>39.8</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="n">
-        <v>35.6</v>
+        <v>36.7</v>
       </c>
       <c r="F10" t="n">
-        <v>38.8</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="11">
@@ -591,19 +591,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000142726595016798</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000433356162188882</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000142726595016798</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000433356162188882</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000000000000000000000000000000293846186365235</v>
+        <v>0.000000000000000000000000000000209432158742956</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000107043583022375</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000323322465769656</v>
       </c>
     </row>
     <row r="12">
@@ -611,17 +611,17 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>28.7</v>
+        <v>29.6</v>
       </c>
       <c r="C12" t="n">
-        <v>28.7</v>
+        <v>29.6</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="n">
-        <v>23.8</v>
+        <v>25.1</v>
       </c>
       <c r="F12" t="n">
-        <v>28.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="13">
@@ -629,19 +629,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000249285234858136</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000377687484965008</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000249285234858136</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000377687484965008</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0000000000322153383887232</v>
+        <v>0.000000000000734494844342164</v>
       </c>
       <c r="F13" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000249285234858136</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000377687484965008</v>
       </c>
     </row>
   </sheetData>
